--- a/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
+++ b/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -662,10 +662,10 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>23550</v>
+        <v>24921</v>
       </c>
       <c r="B17">
-        <v>23550</v>
+        <v>24921</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -673,18 +673,18 @@
         </is>
       </c>
       <c r="D17">
-        <v>3095</v>
+        <v>1724</v>
       </c>
       <c r="E17">
-        <v>3095</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>23386</v>
+        <v>24796</v>
       </c>
       <c r="B18">
-        <v>23386</v>
+        <v>24796</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -692,10 +692,29 @@
         </is>
       </c>
       <c r="D18">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E18">
-        <v>164</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>23957</v>
+      </c>
+      <c r="B19">
+        <v>23957</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Exclude patients with less than one month of exposure</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>839</v>
+      </c>
+      <c r="E19">
+        <v>839</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
+++ b/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
@@ -491,10 +491,10 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>73133</v>
+        <v>73128</v>
       </c>
       <c r="B8">
-        <v>30045</v>
+        <v>30044</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -502,18 +502,18 @@
         </is>
       </c>
       <c r="D8">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E8">
-        <v>2617</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>73122</v>
+        <v>73117</v>
       </c>
       <c r="B9">
-        <v>30040</v>
+        <v>30039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -529,10 +529,10 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>41082</v>
+        <v>41081</v>
       </c>
       <c r="B10">
-        <v>30040</v>
+        <v>30039</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -543,15 +543,15 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>32040</v>
+        <v>32036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>39029</v>
+        <v>39028</v>
       </c>
       <c r="B11">
-        <v>30040</v>
+        <v>30039</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -567,10 +567,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>39029</v>
+        <v>39028</v>
       </c>
       <c r="B12">
-        <v>30040</v>
+        <v>30039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>39029</v>
+        <v>39028</v>
       </c>
       <c r="B13">
-        <v>30040</v>
+        <v>30039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>30039</v>
+        <v>30038</v>
       </c>
       <c r="B14">
-        <v>30039</v>
+        <v>30038</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>26645</v>
+        <v>26644</v>
       </c>
       <c r="B15">
-        <v>26645</v>
+        <v>26644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -643,10 +643,10 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>26645</v>
+        <v>26644</v>
       </c>
       <c r="B16">
-        <v>26645</v>
+        <v>26644</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>24921</v>
+        <v>24920</v>
       </c>
       <c r="B17">
-        <v>24921</v>
+        <v>24920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>24796</v>
+        <v>24795</v>
       </c>
       <c r="B18">
-        <v>24796</v>
+        <v>24795</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -700,10 +700,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>23957</v>
+        <v>23956</v>
       </c>
       <c r="B19">
-        <v>23957</v>
+        <v>23956</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
+++ b/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -529,52 +529,52 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>41081</v>
+        <v>61669</v>
       </c>
       <c r="B10">
         <v>30039</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clean out using washout period</t>
+          <t>Excluding records on the same day for the same person according to hierarchy (Hip, Spine, NHNS)</t>
         </is>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>32036</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>39028</v>
+        <v>61669</v>
       </c>
       <c r="B11">
         <v>30039</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Excluding records on the same day for the same person according to hierarchy (Hip, Spine, NHNS)</t>
+          <t>Excluding not female individuals</t>
         </is>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>2053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>39028</v>
+        <v>61669</v>
       </c>
       <c r="B12">
         <v>30039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Excluding not female individuals</t>
+          <t>Excluding individuals without fracture records</t>
         </is>
       </c>
       <c r="D12">
@@ -586,40 +586,40 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>39028</v>
+        <v>30038</v>
       </c>
       <c r="B13">
-        <v>30039</v>
+        <v>30038</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Excluding individuals without fracture records</t>
+          <t>Excluding index fractures that happen on the last day of observation period</t>
         </is>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>31631</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>30038</v>
+        <v>26644</v>
       </c>
       <c r="B14">
-        <v>30038</v>
+        <v>26644</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excluding index fractures that happen on the last day of observation period</t>
+          <t>Excluding records with insufficient prior observation and/or outside of observation period</t>
         </is>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3394</v>
       </c>
       <c r="E14">
-        <v>8990</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="15">
@@ -631,90 +631,71 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Excluding records with insufficient prior observation and/or outside of observation period</t>
+          <t>Excluding records of index fractures where the subject has not turned 50</t>
         </is>
       </c>
       <c r="D15">
-        <v>3394</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>3394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>26644</v>
+        <v>24920</v>
       </c>
       <c r="B16">
-        <v>26644</v>
+        <v>24920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Excluding records of index fractures where the subject has not turned 50</t>
+          <t>Excluding records happened after cancer</t>
         </is>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1724</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>24920</v>
+        <v>24795</v>
       </c>
       <c r="B17">
-        <v>24920</v>
+        <v>24795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Excluding records happened after cancer</t>
+          <t>Excluding records happened after metabolic bone diseases</t>
         </is>
       </c>
       <c r="D17">
-        <v>1724</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>1724</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Exclude patients with less than one month of exposure</t>
+        </is>
+      </c>
+      <c r="D18">
         <v>24795</v>
       </c>
-      <c r="B18">
+      <c r="E18">
         <v>24795</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Excluding records happened after metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>125</v>
-      </c>
-      <c r="E18">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>23956</v>
-      </c>
-      <c r="B19">
-        <v>23956</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Exclude patients with less than one month of exposure</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>839</v>
-      </c>
-      <c r="E19">
-        <v>839</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
+++ b/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
@@ -681,10 +681,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0</v>
+        <v>17705</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>17705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>24795</v>
+        <v>7090</v>
       </c>
       <c r="E18">
-        <v>24795</v>
+        <v>7090</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
+++ b/OMOP Analysis/Results/AttritionReportCoh_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,7 +422,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Had their 1st fx &gt;= 01/04/2012 and &lt;= 31/03/2018 when they were &gt; 50 years old</t>
+          <t>Had their first fracture in the study period when they were &gt; 50 years old</t>
         </is>
       </c>
       <c r="D4">
@@ -434,147 +434,147 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>85445</v>
+        <v>54923</v>
       </c>
       <c r="B5">
         <v>30847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Excluding fracture happening before the birth year</t>
+          <t>Clean out using washout period</t>
         </is>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30522</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>75811</v>
+        <v>54923</v>
       </c>
       <c r="B6">
         <v>30847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Excluding records that happen outside of study period</t>
+          <t>Excluding trauma fractures</t>
         </is>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>75750</v>
+        <v>54923</v>
       </c>
       <c r="B7">
-        <v>30823</v>
+        <v>30847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Excluding records that happen outside of observation period</t>
+          <t>Excluding fractures happening before the birth year</t>
         </is>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>73128</v>
+        <v>48897</v>
       </c>
       <c r="B8">
-        <v>30044</v>
+        <v>30847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Excluding trauma fractures (same day as trauma codes or 3 distinct fracture sites on the same date</t>
+          <t>Excluding fractures outside of study period</t>
         </is>
       </c>
       <c r="D8">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2622</v>
+        <v>6026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>73117</v>
+        <v>48858</v>
       </c>
       <c r="B9">
-        <v>30039</v>
+        <v>30823</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Excluding fractures on the same day as death or after death</t>
+          <t>Excluding records that happen outside of observation period</t>
         </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>61669</v>
+        <v>48852</v>
       </c>
       <c r="B10">
-        <v>30039</v>
+        <v>30818</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Excluding records on the same day for the same person according to hierarchy (Hip, Spine, NHNS)</t>
+          <t>Excluding fractures on the same day as death or after death</t>
         </is>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>11448</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>61669</v>
+        <v>42424</v>
       </c>
       <c r="B11">
-        <v>30039</v>
+        <v>30818</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Excluding not female individuals</t>
+          <t>Excluding records on the same day for the same person according to hierarchy (Hip, Spine, NHNS)</t>
         </is>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>61669</v>
+        <v>42424</v>
       </c>
       <c r="B12">
-        <v>30039</v>
+        <v>30818</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Excluding individuals without fracture records</t>
+          <t>Excluding not female individuals</t>
         </is>
       </c>
       <c r="D12">
@@ -586,116 +586,135 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>30038</v>
+        <v>42424</v>
       </c>
       <c r="B13">
-        <v>30038</v>
+        <v>30818</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Excluding index fractures that happen on the last day of observation period</t>
+          <t>Excluding individuals without fracture records</t>
         </is>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>31631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>26644</v>
+        <v>42422</v>
       </c>
       <c r="B14">
-        <v>26644</v>
+        <v>30816</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excluding records with insufficient prior observation and/or outside of observation period</t>
+          <t>Excluding individuals with index fracture after end of observation period</t>
         </is>
       </c>
       <c r="D14">
-        <v>3394</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>3394</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>26644</v>
+        <v>37339</v>
       </c>
       <c r="B15">
-        <v>26644</v>
+        <v>27338</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Excluding records of index fractures where the subject has not turned 50</t>
+          <t>Excluding individuals with less than 730 days observation time prior to index date</t>
         </is>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>3478</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>5083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>24920</v>
+        <v>37339</v>
       </c>
       <c r="B16">
-        <v>24920</v>
+        <v>27338</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Excluding records happened after cancer</t>
+          <t>Excluding individuals who had not turned 50 before index date</t>
         </is>
       </c>
       <c r="D16">
-        <v>1724</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>24795</v>
+        <v>35566</v>
       </c>
       <c r="B17">
-        <v>24795</v>
+        <v>25981</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Excluding records happened after metabolic bone diseases</t>
+          <t>Excluding individuals with cancer prior or on index date</t>
         </is>
       </c>
       <c r="D17">
-        <v>125</v>
+        <v>1357</v>
       </c>
       <c r="E17">
-        <v>125</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>17705</v>
+        <v>35436</v>
       </c>
       <c r="B18">
-        <v>17705</v>
+        <v>25884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exclude patients with less than one month of exposure</t>
+          <t>Excluding individuals with metabolic bone diseases prior or on index date</t>
         </is>
       </c>
       <c r="D18">
-        <v>7090</v>
+        <v>97</v>
       </c>
       <c r="E18">
-        <v>7090</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>22900</v>
+      </c>
+      <c r="B19">
+        <v>22900</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Excluding individuals with less than one month exposure</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>2984</v>
+      </c>
+      <c r="E19">
+        <v>12536</v>
       </c>
     </row>
   </sheetData>
